--- a/printing/regression/training_error_results/averaged_data.xlsx
+++ b/printing/regression/training_error_results/averaged_data.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cchih\Desktop\NTHU\MasterThesis\GA\SGM_GA\printing\regression\training_error_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10B417C-778C-4B89-B80A-D22D8F90F92A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BC9DB2C-C9CA-4BB3-ABB5-1B28F481289A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1 (4)" sheetId="11" r:id="rId1"/>
-    <sheet name="Sheet1 (3)" sheetId="10" r:id="rId2"/>
-    <sheet name="Sheet1 (2)" sheetId="5" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (5)" sheetId="12" r:id="rId2"/>
+    <sheet name="Sheet1 (4)" sheetId="11" r:id="rId3"/>
+    <sheet name="Sheet1 (3)" sheetId="10" r:id="rId4"/>
+    <sheet name="Sheet1 (2)" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="17">
   <si>
     <t>Design_s1(mm)</t>
   </si>
@@ -567,6 +568,1587 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:W13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="6" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2">
+        <v>0.6</v>
+      </c>
+      <c r="B2">
+        <v>0.6</v>
+      </c>
+      <c r="C2">
+        <v>0.31058285412302489</v>
+      </c>
+      <c r="D2">
+        <v>75</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <v>75</v>
+      </c>
+      <c r="G2">
+        <v>93.1</v>
+      </c>
+      <c r="H2">
+        <v>0.48351229911538041</v>
+      </c>
+      <c r="I2">
+        <v>0.24457054343076851</v>
+      </c>
+      <c r="J2">
+        <v>0.19414616781745561</v>
+      </c>
+      <c r="K2">
+        <v>0.21254331848455779</v>
+      </c>
+      <c r="L2">
+        <v>74</v>
+      </c>
+      <c r="M2">
+        <v>80.3</v>
+      </c>
+      <c r="N2">
+        <v>75.3</v>
+      </c>
+      <c r="P2" s="4">
+        <f>AVERAGE(L2:O2)</f>
+        <v>76.533333333333346</v>
+      </c>
+      <c r="Q2" s="6">
+        <f>P2/22</f>
+        <v>3.4787878787878794</v>
+      </c>
+      <c r="R2">
+        <v>60</v>
+      </c>
+      <c r="V2">
+        <f>AVERAGE(R2:U2)</f>
+        <v>60</v>
+      </c>
+      <c r="W2" s="6">
+        <f>V2/22</f>
+        <v>2.7272727272727271</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
+      <c r="A3">
+        <v>0.6</v>
+      </c>
+      <c r="B3">
+        <v>0.6</v>
+      </c>
+      <c r="C3">
+        <v>0.6</v>
+      </c>
+      <c r="D3">
+        <v>60.000000000000007</v>
+      </c>
+      <c r="E3">
+        <v>60</v>
+      </c>
+      <c r="F3">
+        <v>59.999999999999993</v>
+      </c>
+      <c r="G3">
+        <v>70.7</v>
+      </c>
+      <c r="H3">
+        <v>0.45901662751675459</v>
+      </c>
+      <c r="I3">
+        <v>0.48174712180640922</v>
+      </c>
+      <c r="J3">
+        <v>0.23497228708045509</v>
+      </c>
+      <c r="K3">
+        <v>0.19708812999417119</v>
+      </c>
+      <c r="L3">
+        <v>59.5</v>
+      </c>
+      <c r="M3">
+        <v>54.1</v>
+      </c>
+      <c r="N3">
+        <v>58.1</v>
+      </c>
+      <c r="O3">
+        <v>54.4</v>
+      </c>
+      <c r="P3" s="4">
+        <f t="shared" ref="P3:P11" si="0">AVERAGE(L3:O3)</f>
+        <v>56.524999999999999</v>
+      </c>
+      <c r="Q3" s="6">
+        <f t="shared" ref="Q3:Q11" si="1">P3/22</f>
+        <v>2.5693181818181818</v>
+      </c>
+      <c r="R3">
+        <v>39</v>
+      </c>
+      <c r="S3">
+        <v>49.1</v>
+      </c>
+      <c r="T3">
+        <v>46.9</v>
+      </c>
+      <c r="V3">
+        <f t="shared" ref="V3:V13" si="2">AVERAGE(R3:U3)</f>
+        <v>45</v>
+      </c>
+      <c r="W3" s="6">
+        <f>V3/22</f>
+        <v>2.0454545454545454</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4">
+        <v>0.6</v>
+      </c>
+      <c r="B4">
+        <v>0.6</v>
+      </c>
+      <c r="C4">
+        <v>0.84852813742385702</v>
+      </c>
+      <c r="D4">
+        <v>45.000000000000007</v>
+      </c>
+      <c r="E4">
+        <v>90</v>
+      </c>
+      <c r="F4">
+        <v>44.999999999999993</v>
+      </c>
+      <c r="G4">
+        <v>54.766666666666673</v>
+      </c>
+      <c r="H4">
+        <v>0.43973557039816641</v>
+      </c>
+      <c r="I4">
+        <v>0.66866016035259024</v>
+      </c>
+      <c r="J4">
+        <v>0.26710738222454372</v>
+      </c>
+      <c r="K4">
+        <v>0.2119764435925153</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="6"/>
+      <c r="R4">
+        <v>49.1</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="2"/>
+        <v>49.1</v>
+      </c>
+      <c r="W4" s="6"/>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5">
+        <v>0.6</v>
+      </c>
+      <c r="B5">
+        <v>0.9</v>
+      </c>
+      <c r="C5">
+        <v>0.48445078585219159</v>
+      </c>
+      <c r="D5">
+        <v>38.261966199709804</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>111.7380338002902</v>
+      </c>
+      <c r="G5">
+        <v>60.633333333333333</v>
+      </c>
+      <c r="H5">
+        <v>0.62929802668878232</v>
+      </c>
+      <c r="I5">
+        <v>0.26950619700589229</v>
+      </c>
+      <c r="J5">
+        <v>0.30077997001159751</v>
+      </c>
+      <c r="K5">
+        <v>0.44368714981957491</v>
+      </c>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="6"/>
+      <c r="R5">
+        <v>35.5</v>
+      </c>
+      <c r="S5">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="T5">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="U5">
+        <v>38</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="2"/>
+        <v>36.5</v>
+      </c>
+      <c r="W5" s="6"/>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6">
+        <v>0.6</v>
+      </c>
+      <c r="B6">
+        <v>0.9</v>
+      </c>
+      <c r="C6">
+        <v>0.79372539331937708</v>
+      </c>
+      <c r="D6">
+        <v>40.893394649130897</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <v>79.106605350869103</v>
+      </c>
+      <c r="G6">
+        <v>51.825000000000003</v>
+      </c>
+      <c r="H6">
+        <v>0.68703573164592169</v>
+      </c>
+      <c r="I6">
+        <v>0.58224553925766087</v>
+      </c>
+      <c r="J6">
+        <v>0.236626964574946</v>
+      </c>
+      <c r="K6">
+        <v>0.26643957163933391</v>
+      </c>
+      <c r="L6">
+        <v>48.4</v>
+      </c>
+      <c r="M6">
+        <v>48.1</v>
+      </c>
+      <c r="N6">
+        <v>51.1</v>
+      </c>
+      <c r="O6">
+        <v>50.1</v>
+      </c>
+      <c r="P6" s="4">
+        <f t="shared" si="0"/>
+        <v>49.424999999999997</v>
+      </c>
+      <c r="Q6" s="6">
+        <f t="shared" si="1"/>
+        <v>2.2465909090909091</v>
+      </c>
+      <c r="R6">
+        <v>28.8</v>
+      </c>
+      <c r="S6">
+        <v>30</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="2"/>
+        <v>29.4</v>
+      </c>
+      <c r="W6" s="6">
+        <f>V6/22</f>
+        <v>1.3363636363636362</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7">
+        <v>0.6</v>
+      </c>
+      <c r="B7">
+        <v>0.9</v>
+      </c>
+      <c r="C7">
+        <v>1.0816653826391971</v>
+      </c>
+      <c r="D7">
+        <v>33.690067525979792</v>
+      </c>
+      <c r="E7">
+        <v>90</v>
+      </c>
+      <c r="F7">
+        <v>56.309932474020208</v>
+      </c>
+      <c r="G7">
+        <v>42.3</v>
+      </c>
+      <c r="H7">
+        <v>0.64949988963032212</v>
+      </c>
+      <c r="I7">
+        <v>0.83851875369502671</v>
+      </c>
+      <c r="J7">
+        <v>0.27833345565704948</v>
+      </c>
+      <c r="K7">
+        <v>0.22478913777023921</v>
+      </c>
+      <c r="L7">
+        <v>59.2</v>
+      </c>
+      <c r="M7">
+        <v>59.7</v>
+      </c>
+      <c r="N7">
+        <v>56.8</v>
+      </c>
+      <c r="P7" s="4">
+        <f t="shared" si="0"/>
+        <v>58.566666666666663</v>
+      </c>
+      <c r="Q7" s="6">
+        <f t="shared" si="1"/>
+        <v>2.6621212121212121</v>
+      </c>
+      <c r="W7" s="6"/>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8">
+        <v>0.9</v>
+      </c>
+      <c r="B8">
+        <v>0.6</v>
+      </c>
+      <c r="C8">
+        <v>0.48445078585219159</v>
+      </c>
+      <c r="D8">
+        <v>111.7380338002902</v>
+      </c>
+      <c r="E8">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <v>38.261966199709839</v>
+      </c>
+      <c r="G8">
+        <v>114.9666666666667</v>
+      </c>
+      <c r="H8">
+        <v>0.54380155735576474</v>
+      </c>
+      <c r="I8">
+        <v>0.4443468229492506</v>
+      </c>
+      <c r="J8">
+        <v>9.3664070917618622E-2</v>
+      </c>
+      <c r="K8">
+        <v>8.2782325865386544E-2</v>
+      </c>
+      <c r="L8">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="M8">
+        <v>71.5</v>
+      </c>
+      <c r="N8">
+        <v>72</v>
+      </c>
+      <c r="P8" s="4">
+        <f t="shared" si="0"/>
+        <v>71.8</v>
+      </c>
+      <c r="Q8" s="6">
+        <f t="shared" si="1"/>
+        <v>3.2636363636363637</v>
+      </c>
+      <c r="R8">
+        <v>77.5</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="2"/>
+        <v>77.5</v>
+      </c>
+      <c r="W8" s="6">
+        <f t="shared" ref="W8:W12" si="3">V8/22</f>
+        <v>3.5227272727272729</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9">
+        <v>0.9</v>
+      </c>
+      <c r="B9">
+        <v>0.6</v>
+      </c>
+      <c r="C9">
+        <v>0.79372539331937708</v>
+      </c>
+      <c r="D9">
+        <v>79.106605350869103</v>
+      </c>
+      <c r="E9">
+        <v>60</v>
+      </c>
+      <c r="F9">
+        <v>40.893394649130897</v>
+      </c>
+      <c r="G9">
+        <v>84.724999999999994</v>
+      </c>
+      <c r="H9">
+        <v>0.52749718423651881</v>
+      </c>
+      <c r="I9">
+        <v>0.70249518324590676</v>
+      </c>
+      <c r="J9">
+        <v>0.120838026071072</v>
+      </c>
+      <c r="K9">
+        <v>0.1149392607649912</v>
+      </c>
+      <c r="L9">
+        <v>56.6</v>
+      </c>
+      <c r="M9">
+        <v>52.3</v>
+      </c>
+      <c r="N9">
+        <v>51.4</v>
+      </c>
+      <c r="O9">
+        <v>49.3</v>
+      </c>
+      <c r="P9" s="4">
+        <f t="shared" si="0"/>
+        <v>52.400000000000006</v>
+      </c>
+      <c r="Q9" s="6">
+        <f t="shared" si="1"/>
+        <v>2.3818181818181823</v>
+      </c>
+      <c r="R9">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="S9">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="T9">
+        <v>32.9</v>
+      </c>
+      <c r="U9">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="2"/>
+        <v>35.25</v>
+      </c>
+      <c r="W9" s="6">
+        <f t="shared" si="3"/>
+        <v>1.6022727272727273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10">
+        <v>0.9</v>
+      </c>
+      <c r="B10">
+        <v>0.6</v>
+      </c>
+      <c r="C10">
+        <v>1.0816653826391971</v>
+      </c>
+      <c r="D10">
+        <v>56.309932474020208</v>
+      </c>
+      <c r="E10">
+        <v>90</v>
+      </c>
+      <c r="F10">
+        <v>33.690067525979792</v>
+      </c>
+      <c r="G10">
+        <v>62.774999999999999</v>
+      </c>
+      <c r="H10">
+        <v>0.49241198817111898</v>
+      </c>
+      <c r="I10">
+        <v>0.94320830392130994</v>
+      </c>
+      <c r="J10">
+        <v>0.1793133527492794</v>
+      </c>
+      <c r="K10">
+        <v>0.1280036144376335</v>
+      </c>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="6"/>
+      <c r="R10">
+        <v>32.4</v>
+      </c>
+      <c r="S10">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="2"/>
+        <v>34.049999999999997</v>
+      </c>
+      <c r="W10" s="6"/>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11">
+        <v>0.9</v>
+      </c>
+      <c r="B11">
+        <v>0.9</v>
+      </c>
+      <c r="C11">
+        <v>0.46587428118453739</v>
+      </c>
+      <c r="D11">
+        <v>75.000000000000014</v>
+      </c>
+      <c r="E11">
+        <v>30</v>
+      </c>
+      <c r="F11">
+        <v>74.999999999999986</v>
+      </c>
+      <c r="G11">
+        <v>81.766666666666666</v>
+      </c>
+      <c r="H11">
+        <v>0.79149877345561148</v>
+      </c>
+      <c r="I11">
+        <v>0.40368699590879459</v>
+      </c>
+      <c r="J11">
+        <v>0.1205569182487017</v>
+      </c>
+      <c r="K11">
+        <v>0.13348512174602031</v>
+      </c>
+      <c r="L11">
+        <v>51.6</v>
+      </c>
+      <c r="M11">
+        <v>53.9</v>
+      </c>
+      <c r="N11">
+        <v>53.2</v>
+      </c>
+      <c r="O11">
+        <v>55.4</v>
+      </c>
+      <c r="P11" s="4">
+        <f t="shared" si="0"/>
+        <v>53.524999999999999</v>
+      </c>
+      <c r="Q11" s="6">
+        <f t="shared" si="1"/>
+        <v>2.4329545454545456</v>
+      </c>
+      <c r="R11">
+        <v>33.5</v>
+      </c>
+      <c r="S11">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="2"/>
+        <v>33.65</v>
+      </c>
+      <c r="W11" s="6">
+        <f t="shared" si="3"/>
+        <v>1.5295454545454545</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12">
+        <v>0.9</v>
+      </c>
+      <c r="B12">
+        <v>0.9</v>
+      </c>
+      <c r="C12">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="D12">
+        <v>59.999999999999993</v>
+      </c>
+      <c r="E12">
+        <v>60</v>
+      </c>
+      <c r="F12">
+        <v>60.000000000000007</v>
+      </c>
+      <c r="G12">
+        <v>65</v>
+      </c>
+      <c r="H12">
+        <v>0.77814030586794569</v>
+      </c>
+      <c r="I12">
+        <v>0.77885827172591937</v>
+      </c>
+      <c r="J12">
+        <v>0.13539965999628301</v>
+      </c>
+      <c r="K12">
+        <v>0.13460192015497621</v>
+      </c>
+      <c r="L12">
+        <v>47.3</v>
+      </c>
+      <c r="M12">
+        <v>47.7</v>
+      </c>
+      <c r="N12">
+        <v>46</v>
+      </c>
+      <c r="O12">
+        <v>47.3</v>
+      </c>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="7"/>
+      <c r="R12">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="S12">
+        <v>29.2</v>
+      </c>
+      <c r="T12">
+        <v>30</v>
+      </c>
+      <c r="U12">
+        <v>32</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="2"/>
+        <v>31.125</v>
+      </c>
+      <c r="W12" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4147727272727273</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13">
+        <v>0.9</v>
+      </c>
+      <c r="B13">
+        <v>0.9</v>
+      </c>
+      <c r="C13">
+        <v>1.272792206135785</v>
+      </c>
+      <c r="D13">
+        <v>44.999999999999979</v>
+      </c>
+      <c r="E13">
+        <v>90</v>
+      </c>
+      <c r="F13">
+        <v>45.000000000000021</v>
+      </c>
+      <c r="G13">
+        <v>50.05</v>
+      </c>
+      <c r="H13">
+        <v>0.74563354580372954</v>
+      </c>
+      <c r="I13">
+        <v>1.1035941042905111</v>
+      </c>
+      <c r="J13">
+        <v>0.17151828224972471</v>
+      </c>
+      <c r="K13">
+        <v>0.13293458342743</v>
+      </c>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="7"/>
+      <c r="R13">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="2"/>
+        <v>36.200000000000003</v>
+      </c>
+      <c r="W13" s="6">
+        <f>V13/22</f>
+        <v>1.6454545454545455</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F73D5965-FE3B-42AE-9BF6-3C52C5374D19}">
+  <dimension ref="A1:W13"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="6" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
+      <c r="A2">
+        <v>0.6</v>
+      </c>
+      <c r="B2">
+        <v>0.6</v>
+      </c>
+      <c r="C2">
+        <v>0.31058285412302489</v>
+      </c>
+      <c r="D2">
+        <v>75</v>
+      </c>
+      <c r="E2">
+        <v>30</v>
+      </c>
+      <c r="F2">
+        <v>75</v>
+      </c>
+      <c r="G2">
+        <v>93.1</v>
+      </c>
+      <c r="H2">
+        <v>0.48351229911538041</v>
+      </c>
+      <c r="I2">
+        <v>0.24457054343076851</v>
+      </c>
+      <c r="J2">
+        <v>0.19414616781745561</v>
+      </c>
+      <c r="K2">
+        <v>0.21254331848455779</v>
+      </c>
+      <c r="L2">
+        <v>74</v>
+      </c>
+      <c r="M2">
+        <v>80.3</v>
+      </c>
+      <c r="N2">
+        <v>75.3</v>
+      </c>
+      <c r="P2" s="4">
+        <f>AVERAGE(L2:O2)</f>
+        <v>76.533333333333346</v>
+      </c>
+      <c r="Q2" s="6">
+        <f>P2/22</f>
+        <v>3.4787878787878794</v>
+      </c>
+      <c r="R2">
+        <v>60</v>
+      </c>
+      <c r="V2">
+        <f>AVERAGE(R2:U2)</f>
+        <v>60</v>
+      </c>
+      <c r="W2" s="6">
+        <f>V2/22</f>
+        <v>2.7272727272727271</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23">
+      <c r="A3">
+        <v>0.6</v>
+      </c>
+      <c r="B3">
+        <v>0.6</v>
+      </c>
+      <c r="C3">
+        <v>0.6</v>
+      </c>
+      <c r="D3">
+        <v>60.000000000000007</v>
+      </c>
+      <c r="E3">
+        <v>60</v>
+      </c>
+      <c r="F3">
+        <v>59.999999999999993</v>
+      </c>
+      <c r="G3">
+        <v>70.7</v>
+      </c>
+      <c r="H3">
+        <v>0.45901662751675459</v>
+      </c>
+      <c r="I3">
+        <v>0.48174712180640922</v>
+      </c>
+      <c r="J3">
+        <v>0.23497228708045509</v>
+      </c>
+      <c r="K3">
+        <v>0.19708812999417119</v>
+      </c>
+      <c r="L3">
+        <v>59.5</v>
+      </c>
+      <c r="M3">
+        <v>54.1</v>
+      </c>
+      <c r="N3">
+        <v>58.1</v>
+      </c>
+      <c r="O3">
+        <v>54.4</v>
+      </c>
+      <c r="P3" s="4">
+        <f t="shared" ref="P3:P11" si="0">AVERAGE(L3:O3)</f>
+        <v>56.524999999999999</v>
+      </c>
+      <c r="Q3" s="6">
+        <f t="shared" ref="Q3:Q11" si="1">P3/22</f>
+        <v>2.5693181818181818</v>
+      </c>
+      <c r="R3">
+        <v>39</v>
+      </c>
+      <c r="S3">
+        <v>49.1</v>
+      </c>
+      <c r="T3">
+        <v>46.9</v>
+      </c>
+      <c r="V3">
+        <f t="shared" ref="V3:V13" si="2">AVERAGE(R3:U3)</f>
+        <v>45</v>
+      </c>
+      <c r="W3" s="6">
+        <f>V3/22</f>
+        <v>2.0454545454545454</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="A4">
+        <v>0.6</v>
+      </c>
+      <c r="B4">
+        <v>0.6</v>
+      </c>
+      <c r="C4">
+        <v>0.84852813742385702</v>
+      </c>
+      <c r="D4">
+        <v>45.000000000000007</v>
+      </c>
+      <c r="E4">
+        <v>90</v>
+      </c>
+      <c r="F4">
+        <v>44.999999999999993</v>
+      </c>
+      <c r="G4">
+        <v>54.766666666666673</v>
+      </c>
+      <c r="H4">
+        <v>0.43973557039816641</v>
+      </c>
+      <c r="I4">
+        <v>0.66866016035259024</v>
+      </c>
+      <c r="J4">
+        <v>0.26710738222454372</v>
+      </c>
+      <c r="K4">
+        <v>0.2119764435925153</v>
+      </c>
+      <c r="P4" s="4"/>
+      <c r="Q4" s="6"/>
+      <c r="R4">
+        <v>49.1</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="2"/>
+        <v>49.1</v>
+      </c>
+      <c r="W4" s="6"/>
+    </row>
+    <row r="5" spans="1:23">
+      <c r="A5">
+        <v>0.6</v>
+      </c>
+      <c r="B5">
+        <v>0.9</v>
+      </c>
+      <c r="C5">
+        <v>0.48445078585219159</v>
+      </c>
+      <c r="D5">
+        <v>38.261966199709804</v>
+      </c>
+      <c r="E5">
+        <v>30</v>
+      </c>
+      <c r="F5">
+        <v>111.7380338002902</v>
+      </c>
+      <c r="G5">
+        <v>60.633333333333333</v>
+      </c>
+      <c r="H5">
+        <v>0.62929802668878232</v>
+      </c>
+      <c r="I5">
+        <v>0.26950619700589229</v>
+      </c>
+      <c r="J5">
+        <v>0.30077997001159751</v>
+      </c>
+      <c r="K5">
+        <v>0.44368714981957491</v>
+      </c>
+      <c r="P5" s="4"/>
+      <c r="Q5" s="6"/>
+      <c r="R5">
+        <v>35.5</v>
+      </c>
+      <c r="S5">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="T5">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="U5">
+        <v>38</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="2"/>
+        <v>36.5</v>
+      </c>
+      <c r="W5" s="6"/>
+    </row>
+    <row r="6" spans="1:23">
+      <c r="A6">
+        <v>0.6</v>
+      </c>
+      <c r="B6">
+        <v>0.9</v>
+      </c>
+      <c r="C6">
+        <v>0.79372539331937708</v>
+      </c>
+      <c r="D6">
+        <v>40.893394649130897</v>
+      </c>
+      <c r="E6">
+        <v>60</v>
+      </c>
+      <c r="F6">
+        <v>79.106605350869103</v>
+      </c>
+      <c r="G6">
+        <v>51.825000000000003</v>
+      </c>
+      <c r="H6">
+        <v>0.68703573164592169</v>
+      </c>
+      <c r="I6">
+        <v>0.58224553925766087</v>
+      </c>
+      <c r="J6">
+        <v>0.236626964574946</v>
+      </c>
+      <c r="K6">
+        <v>0.26643957163933391</v>
+      </c>
+      <c r="L6">
+        <v>48.4</v>
+      </c>
+      <c r="M6">
+        <v>48.1</v>
+      </c>
+      <c r="N6">
+        <v>51.1</v>
+      </c>
+      <c r="O6">
+        <v>50.1</v>
+      </c>
+      <c r="P6" s="4">
+        <f t="shared" si="0"/>
+        <v>49.424999999999997</v>
+      </c>
+      <c r="Q6" s="6">
+        <f t="shared" si="1"/>
+        <v>2.2465909090909091</v>
+      </c>
+      <c r="R6">
+        <v>28.8</v>
+      </c>
+      <c r="S6">
+        <v>30</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="2"/>
+        <v>29.4</v>
+      </c>
+      <c r="W6" s="6">
+        <f>V6/22</f>
+        <v>1.3363636363636362</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
+      <c r="A7">
+        <v>0.6</v>
+      </c>
+      <c r="B7">
+        <v>0.9</v>
+      </c>
+      <c r="C7">
+        <v>1.0816653826391971</v>
+      </c>
+      <c r="D7">
+        <v>33.690067525979792</v>
+      </c>
+      <c r="E7">
+        <v>90</v>
+      </c>
+      <c r="F7">
+        <v>56.309932474020208</v>
+      </c>
+      <c r="G7">
+        <v>42.3</v>
+      </c>
+      <c r="H7">
+        <v>0.64949988963032212</v>
+      </c>
+      <c r="I7">
+        <v>0.83851875369502671</v>
+      </c>
+      <c r="J7">
+        <v>0.27833345565704948</v>
+      </c>
+      <c r="K7">
+        <v>0.22478913777023921</v>
+      </c>
+      <c r="L7">
+        <v>59.2</v>
+      </c>
+      <c r="M7">
+        <v>59.7</v>
+      </c>
+      <c r="N7">
+        <v>56.8</v>
+      </c>
+      <c r="P7" s="4">
+        <f t="shared" si="0"/>
+        <v>58.566666666666663</v>
+      </c>
+      <c r="Q7" s="6">
+        <f t="shared" si="1"/>
+        <v>2.6621212121212121</v>
+      </c>
+      <c r="W7" s="6"/>
+    </row>
+    <row r="8" spans="1:23">
+      <c r="A8">
+        <v>0.9</v>
+      </c>
+      <c r="B8">
+        <v>0.6</v>
+      </c>
+      <c r="C8">
+        <v>0.48445078585219159</v>
+      </c>
+      <c r="D8">
+        <v>111.7380338002902</v>
+      </c>
+      <c r="E8">
+        <v>30</v>
+      </c>
+      <c r="F8">
+        <v>38.261966199709839</v>
+      </c>
+      <c r="G8">
+        <v>114.9666666666667</v>
+      </c>
+      <c r="H8">
+        <v>0.54380155735576474</v>
+      </c>
+      <c r="I8">
+        <v>0.4443468229492506</v>
+      </c>
+      <c r="J8">
+        <v>9.3664070917618622E-2</v>
+      </c>
+      <c r="K8">
+        <v>8.2782325865386544E-2</v>
+      </c>
+      <c r="L8">
+        <v>71.900000000000006</v>
+      </c>
+      <c r="M8">
+        <v>71.5</v>
+      </c>
+      <c r="N8">
+        <v>72</v>
+      </c>
+      <c r="P8" s="4">
+        <f t="shared" si="0"/>
+        <v>71.8</v>
+      </c>
+      <c r="Q8" s="6">
+        <f t="shared" si="1"/>
+        <v>3.2636363636363637</v>
+      </c>
+      <c r="R8">
+        <v>77.5</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="2"/>
+        <v>77.5</v>
+      </c>
+      <c r="W8" s="6">
+        <f t="shared" ref="W8:W12" si="3">V8/22</f>
+        <v>3.5227272727272729</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
+      <c r="A9">
+        <v>0.9</v>
+      </c>
+      <c r="B9">
+        <v>0.6</v>
+      </c>
+      <c r="C9">
+        <v>0.79372539331937708</v>
+      </c>
+      <c r="D9">
+        <v>79.106605350869103</v>
+      </c>
+      <c r="E9">
+        <v>60</v>
+      </c>
+      <c r="F9">
+        <v>40.893394649130897</v>
+      </c>
+      <c r="G9">
+        <v>84.724999999999994</v>
+      </c>
+      <c r="H9">
+        <v>0.52749718423651881</v>
+      </c>
+      <c r="I9">
+        <v>0.70249518324590676</v>
+      </c>
+      <c r="J9">
+        <v>0.120838026071072</v>
+      </c>
+      <c r="K9">
+        <v>0.1149392607649912</v>
+      </c>
+      <c r="L9">
+        <v>56.6</v>
+      </c>
+      <c r="M9">
+        <v>52.3</v>
+      </c>
+      <c r="N9">
+        <v>51.4</v>
+      </c>
+      <c r="O9">
+        <v>49.3</v>
+      </c>
+      <c r="P9" s="4">
+        <f t="shared" si="0"/>
+        <v>52.400000000000006</v>
+      </c>
+      <c r="Q9" s="6">
+        <f t="shared" si="1"/>
+        <v>2.3818181818181823</v>
+      </c>
+      <c r="R9">
+        <v>34.200000000000003</v>
+      </c>
+      <c r="S9">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="T9">
+        <v>32.9</v>
+      </c>
+      <c r="U9">
+        <v>33.700000000000003</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="2"/>
+        <v>35.25</v>
+      </c>
+      <c r="W9" s="6">
+        <f t="shared" si="3"/>
+        <v>1.6022727272727273</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
+      <c r="A10">
+        <v>0.9</v>
+      </c>
+      <c r="B10">
+        <v>0.6</v>
+      </c>
+      <c r="C10">
+        <v>1.0816653826391971</v>
+      </c>
+      <c r="D10">
+        <v>56.309932474020208</v>
+      </c>
+      <c r="E10">
+        <v>90</v>
+      </c>
+      <c r="F10">
+        <v>33.690067525979792</v>
+      </c>
+      <c r="G10">
+        <v>62.774999999999999</v>
+      </c>
+      <c r="H10">
+        <v>0.49241198817111898</v>
+      </c>
+      <c r="I10">
+        <v>0.94320830392130994</v>
+      </c>
+      <c r="J10">
+        <v>0.1793133527492794</v>
+      </c>
+      <c r="K10">
+        <v>0.1280036144376335</v>
+      </c>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="6"/>
+      <c r="R10">
+        <v>32.4</v>
+      </c>
+      <c r="S10">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="2"/>
+        <v>34.049999999999997</v>
+      </c>
+      <c r="W10" s="6"/>
+    </row>
+    <row r="11" spans="1:23">
+      <c r="A11">
+        <v>0.9</v>
+      </c>
+      <c r="B11">
+        <v>0.9</v>
+      </c>
+      <c r="C11">
+        <v>0.46587428118453739</v>
+      </c>
+      <c r="D11">
+        <v>75.000000000000014</v>
+      </c>
+      <c r="E11">
+        <v>30</v>
+      </c>
+      <c r="F11">
+        <v>74.999999999999986</v>
+      </c>
+      <c r="G11">
+        <v>81.766666666666666</v>
+      </c>
+      <c r="H11">
+        <v>0.79149877345561148</v>
+      </c>
+      <c r="I11">
+        <v>0.40368699590879459</v>
+      </c>
+      <c r="J11">
+        <v>0.1205569182487017</v>
+      </c>
+      <c r="K11">
+        <v>0.13348512174602031</v>
+      </c>
+      <c r="L11">
+        <v>51.6</v>
+      </c>
+      <c r="M11">
+        <v>53.9</v>
+      </c>
+      <c r="N11">
+        <v>53.2</v>
+      </c>
+      <c r="O11">
+        <v>55.4</v>
+      </c>
+      <c r="P11" s="4">
+        <f t="shared" si="0"/>
+        <v>53.524999999999999</v>
+      </c>
+      <c r="Q11" s="6">
+        <f t="shared" si="1"/>
+        <v>2.4329545454545456</v>
+      </c>
+      <c r="R11">
+        <v>33.5</v>
+      </c>
+      <c r="S11">
+        <v>33.799999999999997</v>
+      </c>
+      <c r="V11">
+        <f t="shared" si="2"/>
+        <v>33.65</v>
+      </c>
+      <c r="W11" s="6">
+        <f t="shared" si="3"/>
+        <v>1.5295454545454545</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
+      <c r="A12">
+        <v>0.9</v>
+      </c>
+      <c r="B12">
+        <v>0.9</v>
+      </c>
+      <c r="C12">
+        <v>0.89999999999999991</v>
+      </c>
+      <c r="D12">
+        <v>59.999999999999993</v>
+      </c>
+      <c r="E12">
+        <v>60</v>
+      </c>
+      <c r="F12">
+        <v>60.000000000000007</v>
+      </c>
+      <c r="G12">
+        <v>65</v>
+      </c>
+      <c r="H12">
+        <v>0.77814030586794569</v>
+      </c>
+      <c r="I12">
+        <v>0.77885827172591937</v>
+      </c>
+      <c r="J12">
+        <v>0.13539965999628301</v>
+      </c>
+      <c r="K12">
+        <v>0.13460192015497621</v>
+      </c>
+      <c r="L12">
+        <v>47.3</v>
+      </c>
+      <c r="M12">
+        <v>47.7</v>
+      </c>
+      <c r="N12">
+        <v>46</v>
+      </c>
+      <c r="O12">
+        <v>47.3</v>
+      </c>
+      <c r="P12" s="4"/>
+      <c r="Q12" s="7"/>
+      <c r="R12">
+        <v>33.299999999999997</v>
+      </c>
+      <c r="S12">
+        <v>29.2</v>
+      </c>
+      <c r="T12">
+        <v>30</v>
+      </c>
+      <c r="U12">
+        <v>32</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="2"/>
+        <v>31.125</v>
+      </c>
+      <c r="W12" s="6">
+        <f t="shared" si="3"/>
+        <v>1.4147727272727273</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
+      <c r="A13">
+        <v>0.9</v>
+      </c>
+      <c r="B13">
+        <v>0.9</v>
+      </c>
+      <c r="C13">
+        <v>1.272792206135785</v>
+      </c>
+      <c r="D13">
+        <v>44.999999999999979</v>
+      </c>
+      <c r="E13">
+        <v>90</v>
+      </c>
+      <c r="F13">
+        <v>45.000000000000021</v>
+      </c>
+      <c r="G13">
+        <v>50.05</v>
+      </c>
+      <c r="H13">
+        <v>0.74563354580372954</v>
+      </c>
+      <c r="I13">
+        <v>1.1035941042905111</v>
+      </c>
+      <c r="J13">
+        <v>0.17151828224972471</v>
+      </c>
+      <c r="K13">
+        <v>0.13293458342743</v>
+      </c>
+      <c r="P13" s="4"/>
+      <c r="Q13" s="7"/>
+      <c r="R13">
+        <v>36.200000000000003</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="2"/>
+        <v>36.200000000000003</v>
+      </c>
+      <c r="W13" s="6">
+        <f>V13/22</f>
+        <v>1.6454545454545455</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8769C09C-C53B-4D4E-B105-51033AAB2610}">
   <dimension ref="A1:U13"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -972,7 +2554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69AF1656-33D3-474F-86E9-AAFFBFCFE5E3}">
   <dimension ref="A1:U15"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1477,7 +3059,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D320D722-306F-4B64-A89A-132A087F6E59}">
   <dimension ref="A1:W15"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2015,794 +3597,4 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="6" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:23">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23">
-      <c r="A2">
-        <v>0.6</v>
-      </c>
-      <c r="B2">
-        <v>0.6</v>
-      </c>
-      <c r="C2">
-        <v>0.31058285412302489</v>
-      </c>
-      <c r="D2">
-        <v>75</v>
-      </c>
-      <c r="E2">
-        <v>30</v>
-      </c>
-      <c r="F2">
-        <v>75</v>
-      </c>
-      <c r="G2">
-        <v>93.1</v>
-      </c>
-      <c r="H2">
-        <v>0.48351229911538041</v>
-      </c>
-      <c r="I2">
-        <v>0.24457054343076851</v>
-      </c>
-      <c r="J2">
-        <v>0.19414616781745561</v>
-      </c>
-      <c r="K2">
-        <v>0.21254331848455779</v>
-      </c>
-      <c r="L2">
-        <v>74</v>
-      </c>
-      <c r="M2">
-        <v>80.3</v>
-      </c>
-      <c r="N2">
-        <v>75.3</v>
-      </c>
-      <c r="P2" s="4">
-        <f>AVERAGE(L2:O2)</f>
-        <v>76.533333333333346</v>
-      </c>
-      <c r="Q2" s="6">
-        <f>P2/22</f>
-        <v>3.4787878787878794</v>
-      </c>
-      <c r="R2">
-        <v>60</v>
-      </c>
-      <c r="V2">
-        <f>AVERAGE(R2:U2)</f>
-        <v>60</v>
-      </c>
-      <c r="W2" s="6">
-        <f>V2/22</f>
-        <v>2.7272727272727271</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23">
-      <c r="A3">
-        <v>0.6</v>
-      </c>
-      <c r="B3">
-        <v>0.6</v>
-      </c>
-      <c r="C3">
-        <v>0.6</v>
-      </c>
-      <c r="D3">
-        <v>60.000000000000007</v>
-      </c>
-      <c r="E3">
-        <v>60</v>
-      </c>
-      <c r="F3">
-        <v>59.999999999999993</v>
-      </c>
-      <c r="G3">
-        <v>70.7</v>
-      </c>
-      <c r="H3">
-        <v>0.45901662751675459</v>
-      </c>
-      <c r="I3">
-        <v>0.48174712180640922</v>
-      </c>
-      <c r="J3">
-        <v>0.23497228708045509</v>
-      </c>
-      <c r="K3">
-        <v>0.19708812999417119</v>
-      </c>
-      <c r="L3">
-        <v>59.5</v>
-      </c>
-      <c r="M3">
-        <v>54.1</v>
-      </c>
-      <c r="N3">
-        <v>58.1</v>
-      </c>
-      <c r="O3">
-        <v>54.4</v>
-      </c>
-      <c r="P3" s="4">
-        <f t="shared" ref="P3:P11" si="0">AVERAGE(L3:O3)</f>
-        <v>56.524999999999999</v>
-      </c>
-      <c r="Q3" s="6">
-        <f t="shared" ref="Q3:Q11" si="1">P3/22</f>
-        <v>2.5693181818181818</v>
-      </c>
-      <c r="R3">
-        <v>39</v>
-      </c>
-      <c r="S3">
-        <v>49.1</v>
-      </c>
-      <c r="T3">
-        <v>46.9</v>
-      </c>
-      <c r="V3">
-        <f t="shared" ref="V3:V13" si="2">AVERAGE(R3:U3)</f>
-        <v>45</v>
-      </c>
-      <c r="W3" s="6">
-        <f>V3/22</f>
-        <v>2.0454545454545454</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23">
-      <c r="A4">
-        <v>0.6</v>
-      </c>
-      <c r="B4">
-        <v>0.6</v>
-      </c>
-      <c r="C4">
-        <v>0.84852813742385702</v>
-      </c>
-      <c r="D4">
-        <v>45.000000000000007</v>
-      </c>
-      <c r="E4">
-        <v>90</v>
-      </c>
-      <c r="F4">
-        <v>44.999999999999993</v>
-      </c>
-      <c r="G4">
-        <v>54.766666666666673</v>
-      </c>
-      <c r="H4">
-        <v>0.43973557039816641</v>
-      </c>
-      <c r="I4">
-        <v>0.66866016035259024</v>
-      </c>
-      <c r="J4">
-        <v>0.26710738222454372</v>
-      </c>
-      <c r="K4">
-        <v>0.2119764435925153</v>
-      </c>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="6"/>
-      <c r="R4">
-        <v>49.1</v>
-      </c>
-      <c r="V4">
-        <f t="shared" si="2"/>
-        <v>49.1</v>
-      </c>
-      <c r="W4" s="6"/>
-    </row>
-    <row r="5" spans="1:23">
-      <c r="A5">
-        <v>0.6</v>
-      </c>
-      <c r="B5">
-        <v>0.9</v>
-      </c>
-      <c r="C5">
-        <v>0.48445078585219159</v>
-      </c>
-      <c r="D5">
-        <v>38.261966199709804</v>
-      </c>
-      <c r="E5">
-        <v>30</v>
-      </c>
-      <c r="F5">
-        <v>111.7380338002902</v>
-      </c>
-      <c r="G5">
-        <v>60.633333333333333</v>
-      </c>
-      <c r="H5">
-        <v>0.62929802668878232</v>
-      </c>
-      <c r="I5">
-        <v>0.26950619700589229</v>
-      </c>
-      <c r="J5">
-        <v>0.30077997001159751</v>
-      </c>
-      <c r="K5">
-        <v>0.44368714981957491</v>
-      </c>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="6"/>
-      <c r="R5">
-        <v>35.5</v>
-      </c>
-      <c r="S5">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="T5">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="U5">
-        <v>38</v>
-      </c>
-      <c r="V5">
-        <f t="shared" si="2"/>
-        <v>36.5</v>
-      </c>
-      <c r="W5" s="6"/>
-    </row>
-    <row r="6" spans="1:23">
-      <c r="A6">
-        <v>0.6</v>
-      </c>
-      <c r="B6">
-        <v>0.9</v>
-      </c>
-      <c r="C6">
-        <v>0.79372539331937708</v>
-      </c>
-      <c r="D6">
-        <v>40.893394649130897</v>
-      </c>
-      <c r="E6">
-        <v>60</v>
-      </c>
-      <c r="F6">
-        <v>79.106605350869103</v>
-      </c>
-      <c r="G6">
-        <v>51.825000000000003</v>
-      </c>
-      <c r="H6">
-        <v>0.68703573164592169</v>
-      </c>
-      <c r="I6">
-        <v>0.58224553925766087</v>
-      </c>
-      <c r="J6">
-        <v>0.236626964574946</v>
-      </c>
-      <c r="K6">
-        <v>0.26643957163933391</v>
-      </c>
-      <c r="L6">
-        <v>48.4</v>
-      </c>
-      <c r="M6">
-        <v>48.1</v>
-      </c>
-      <c r="N6">
-        <v>51.1</v>
-      </c>
-      <c r="O6">
-        <v>50.1</v>
-      </c>
-      <c r="P6" s="4">
-        <f t="shared" si="0"/>
-        <v>49.424999999999997</v>
-      </c>
-      <c r="Q6" s="6">
-        <f t="shared" si="1"/>
-        <v>2.2465909090909091</v>
-      </c>
-      <c r="R6">
-        <v>28.8</v>
-      </c>
-      <c r="S6">
-        <v>30</v>
-      </c>
-      <c r="V6">
-        <f t="shared" si="2"/>
-        <v>29.4</v>
-      </c>
-      <c r="W6" s="6">
-        <f>V6/22</f>
-        <v>1.3363636363636362</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23">
-      <c r="A7">
-        <v>0.6</v>
-      </c>
-      <c r="B7">
-        <v>0.9</v>
-      </c>
-      <c r="C7">
-        <v>1.0816653826391971</v>
-      </c>
-      <c r="D7">
-        <v>33.690067525979792</v>
-      </c>
-      <c r="E7">
-        <v>90</v>
-      </c>
-      <c r="F7">
-        <v>56.309932474020208</v>
-      </c>
-      <c r="G7">
-        <v>42.3</v>
-      </c>
-      <c r="H7">
-        <v>0.64949988963032212</v>
-      </c>
-      <c r="I7">
-        <v>0.83851875369502671</v>
-      </c>
-      <c r="J7">
-        <v>0.27833345565704948</v>
-      </c>
-      <c r="K7">
-        <v>0.22478913777023921</v>
-      </c>
-      <c r="L7">
-        <v>59.2</v>
-      </c>
-      <c r="M7">
-        <v>59.7</v>
-      </c>
-      <c r="N7">
-        <v>56.8</v>
-      </c>
-      <c r="P7" s="4">
-        <f t="shared" si="0"/>
-        <v>58.566666666666663</v>
-      </c>
-      <c r="Q7" s="6">
-        <f t="shared" si="1"/>
-        <v>2.6621212121212121</v>
-      </c>
-      <c r="W7" s="6"/>
-    </row>
-    <row r="8" spans="1:23">
-      <c r="A8">
-        <v>0.9</v>
-      </c>
-      <c r="B8">
-        <v>0.6</v>
-      </c>
-      <c r="C8">
-        <v>0.48445078585219159</v>
-      </c>
-      <c r="D8">
-        <v>111.7380338002902</v>
-      </c>
-      <c r="E8">
-        <v>30</v>
-      </c>
-      <c r="F8">
-        <v>38.261966199709839</v>
-      </c>
-      <c r="G8">
-        <v>114.9666666666667</v>
-      </c>
-      <c r="H8">
-        <v>0.54380155735576474</v>
-      </c>
-      <c r="I8">
-        <v>0.4443468229492506</v>
-      </c>
-      <c r="J8">
-        <v>9.3664070917618622E-2</v>
-      </c>
-      <c r="K8">
-        <v>8.2782325865386544E-2</v>
-      </c>
-      <c r="L8">
-        <v>71.900000000000006</v>
-      </c>
-      <c r="M8">
-        <v>71.5</v>
-      </c>
-      <c r="N8">
-        <v>72</v>
-      </c>
-      <c r="P8" s="4">
-        <f t="shared" si="0"/>
-        <v>71.8</v>
-      </c>
-      <c r="Q8" s="6">
-        <f t="shared" si="1"/>
-        <v>3.2636363636363637</v>
-      </c>
-      <c r="R8">
-        <v>77.5</v>
-      </c>
-      <c r="V8">
-        <f t="shared" si="2"/>
-        <v>77.5</v>
-      </c>
-      <c r="W8" s="6">
-        <f t="shared" ref="W8:W12" si="3">V8/22</f>
-        <v>3.5227272727272729</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23">
-      <c r="A9">
-        <v>0.9</v>
-      </c>
-      <c r="B9">
-        <v>0.6</v>
-      </c>
-      <c r="C9">
-        <v>0.79372539331937708</v>
-      </c>
-      <c r="D9">
-        <v>79.106605350869103</v>
-      </c>
-      <c r="E9">
-        <v>60</v>
-      </c>
-      <c r="F9">
-        <v>40.893394649130897</v>
-      </c>
-      <c r="G9">
-        <v>84.724999999999994</v>
-      </c>
-      <c r="H9">
-        <v>0.52749718423651881</v>
-      </c>
-      <c r="I9">
-        <v>0.70249518324590676</v>
-      </c>
-      <c r="J9">
-        <v>0.120838026071072</v>
-      </c>
-      <c r="K9">
-        <v>0.1149392607649912</v>
-      </c>
-      <c r="L9">
-        <v>56.6</v>
-      </c>
-      <c r="M9">
-        <v>52.3</v>
-      </c>
-      <c r="N9">
-        <v>51.4</v>
-      </c>
-      <c r="O9">
-        <v>49.3</v>
-      </c>
-      <c r="P9" s="4">
-        <f t="shared" si="0"/>
-        <v>52.400000000000006</v>
-      </c>
-      <c r="Q9" s="6">
-        <f t="shared" si="1"/>
-        <v>2.3818181818181823</v>
-      </c>
-      <c r="R9">
-        <v>34.200000000000003</v>
-      </c>
-      <c r="S9">
-        <v>40.200000000000003</v>
-      </c>
-      <c r="T9">
-        <v>32.9</v>
-      </c>
-      <c r="U9">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="2"/>
-        <v>35.25</v>
-      </c>
-      <c r="W9" s="6">
-        <f t="shared" si="3"/>
-        <v>1.6022727272727273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23">
-      <c r="A10">
-        <v>0.9</v>
-      </c>
-      <c r="B10">
-        <v>0.6</v>
-      </c>
-      <c r="C10">
-        <v>1.0816653826391971</v>
-      </c>
-      <c r="D10">
-        <v>56.309932474020208</v>
-      </c>
-      <c r="E10">
-        <v>90</v>
-      </c>
-      <c r="F10">
-        <v>33.690067525979792</v>
-      </c>
-      <c r="G10">
-        <v>62.774999999999999</v>
-      </c>
-      <c r="H10">
-        <v>0.49241198817111898</v>
-      </c>
-      <c r="I10">
-        <v>0.94320830392130994</v>
-      </c>
-      <c r="J10">
-        <v>0.1793133527492794</v>
-      </c>
-      <c r="K10">
-        <v>0.1280036144376335</v>
-      </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="6"/>
-      <c r="R10">
-        <v>32.4</v>
-      </c>
-      <c r="S10">
-        <v>35.700000000000003</v>
-      </c>
-      <c r="V10">
-        <f t="shared" si="2"/>
-        <v>34.049999999999997</v>
-      </c>
-      <c r="W10" s="6"/>
-    </row>
-    <row r="11" spans="1:23">
-      <c r="A11">
-        <v>0.9</v>
-      </c>
-      <c r="B11">
-        <v>0.9</v>
-      </c>
-      <c r="C11">
-        <v>0.46587428118453739</v>
-      </c>
-      <c r="D11">
-        <v>75.000000000000014</v>
-      </c>
-      <c r="E11">
-        <v>30</v>
-      </c>
-      <c r="F11">
-        <v>74.999999999999986</v>
-      </c>
-      <c r="G11">
-        <v>81.766666666666666</v>
-      </c>
-      <c r="H11">
-        <v>0.79149877345561148</v>
-      </c>
-      <c r="I11">
-        <v>0.40368699590879459</v>
-      </c>
-      <c r="J11">
-        <v>0.1205569182487017</v>
-      </c>
-      <c r="K11">
-        <v>0.13348512174602031</v>
-      </c>
-      <c r="L11">
-        <v>51.6</v>
-      </c>
-      <c r="M11">
-        <v>53.9</v>
-      </c>
-      <c r="N11">
-        <v>53.2</v>
-      </c>
-      <c r="O11">
-        <v>55.4</v>
-      </c>
-      <c r="P11" s="4">
-        <f t="shared" si="0"/>
-        <v>53.524999999999999</v>
-      </c>
-      <c r="Q11" s="6">
-        <f t="shared" si="1"/>
-        <v>2.4329545454545456</v>
-      </c>
-      <c r="R11">
-        <v>33.5</v>
-      </c>
-      <c r="S11">
-        <v>33.799999999999997</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="2"/>
-        <v>33.65</v>
-      </c>
-      <c r="W11" s="6">
-        <f t="shared" si="3"/>
-        <v>1.5295454545454545</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23">
-      <c r="A12">
-        <v>0.9</v>
-      </c>
-      <c r="B12">
-        <v>0.9</v>
-      </c>
-      <c r="C12">
-        <v>0.89999999999999991</v>
-      </c>
-      <c r="D12">
-        <v>59.999999999999993</v>
-      </c>
-      <c r="E12">
-        <v>60</v>
-      </c>
-      <c r="F12">
-        <v>60.000000000000007</v>
-      </c>
-      <c r="G12">
-        <v>65</v>
-      </c>
-      <c r="H12">
-        <v>0.77814030586794569</v>
-      </c>
-      <c r="I12">
-        <v>0.77885827172591937</v>
-      </c>
-      <c r="J12">
-        <v>0.13539965999628301</v>
-      </c>
-      <c r="K12">
-        <v>0.13460192015497621</v>
-      </c>
-      <c r="L12">
-        <v>47.3</v>
-      </c>
-      <c r="M12">
-        <v>47.7</v>
-      </c>
-      <c r="N12">
-        <v>46</v>
-      </c>
-      <c r="O12">
-        <v>47.3</v>
-      </c>
-      <c r="P12" s="4"/>
-      <c r="Q12" s="7"/>
-      <c r="R12">
-        <v>33.299999999999997</v>
-      </c>
-      <c r="S12">
-        <v>29.2</v>
-      </c>
-      <c r="T12">
-        <v>30</v>
-      </c>
-      <c r="U12">
-        <v>32</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="2"/>
-        <v>31.125</v>
-      </c>
-      <c r="W12" s="6">
-        <f t="shared" si="3"/>
-        <v>1.4147727272727273</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23">
-      <c r="A13">
-        <v>0.9</v>
-      </c>
-      <c r="B13">
-        <v>0.9</v>
-      </c>
-      <c r="C13">
-        <v>1.272792206135785</v>
-      </c>
-      <c r="D13">
-        <v>44.999999999999979</v>
-      </c>
-      <c r="E13">
-        <v>90</v>
-      </c>
-      <c r="F13">
-        <v>45.000000000000021</v>
-      </c>
-      <c r="G13">
-        <v>50.05</v>
-      </c>
-      <c r="H13">
-        <v>0.74563354580372954</v>
-      </c>
-      <c r="I13">
-        <v>1.1035941042905111</v>
-      </c>
-      <c r="J13">
-        <v>0.17151828224972471</v>
-      </c>
-      <c r="K13">
-        <v>0.13293458342743</v>
-      </c>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="7"/>
-      <c r="R13">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="2"/>
-        <v>36.200000000000003</v>
-      </c>
-      <c r="W13" s="6">
-        <f>V13/22</f>
-        <v>1.6454545454545455</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>